--- a/data/checklists/nba/1991-92-Hoops-Basketball.xlsx
+++ b/data/checklists/nba/1991-92-Hoops-Basketball.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D587"/>
+  <dimension ref="A1:D609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10918,6 +10918,402 @@
       </c>
       <c r="D587" t="inlineStr"/>
     </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>Isiah Thomas</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>MVP All-Stars</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr"/>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>Tom Chambers</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Seattle SuperSonics</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>MVP All-Stars</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr"/>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>Michael Jordan</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>MVP All-Stars</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr"/>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>Karl Malone</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>MVP All-Stars</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr"/>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>Magic Johnson</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>MVP All-Stars</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr"/>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>Charles Barkley</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>MVP All-Stars</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr"/>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>Larry Nance</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>Slam Dunk Champions</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr"/>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>Dominique Wilkins</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>Slam Dunk Champions</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr"/>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>Spud Webb</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>Slam Dunk Champions</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr"/>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>Michael Jordan</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>Slam Dunk Champions</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr"/>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>Kenny Walker</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>Slam Dunk Champions</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr"/>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>Dee Brown</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>Slam Dunk Champions</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr"/>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>Sidney Moncrief</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>Prototypes - PROTO</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr"/>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>Larry Bird</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>Prototypes - PROTO</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr"/>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>Muggsy Bogues</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>Prototypes - PROTO</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr"/>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>Alvin Robertson</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>Prototypes - PROTO</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr"/>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>Chris Dudley</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>New Jersey Nets</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>Prototypes - PROTO</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr"/>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>Charles Oakley</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>Prototypes - PROTO</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr"/>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>Jerry Reynolds</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>Prototypes - PROTO</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr"/>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>Armon Gilliam</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>Prototypes - PROTO</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr"/>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>Sedale Threatt</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Seattle SuperSonics</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>Prototypes - PROTO</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr"/>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>Jeff Malone</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>Prototypes - PROTO</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
